--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6AC03DA-6BCC-476F-BEA8-7354E7C240FA}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90EB3A4F-78A5-4A2D-9306-6C5688BF67BC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>As, I had an exam today ,and had to travel afterward. I was a little tired, but I managed to complete my momentous tasks and get some rest.</t>
+  </si>
+  <si>
+    <t>Hectic day, stuck in heavy traffic and had a very busy schedule.</t>
   </si>
 </sst>
 </file>
@@ -1084,27 +1087,51 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>120</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90EB3A4F-78A5-4A2D-9306-6C5688BF67BC}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1726E68-D7BC-4274-B769-F7D87935900A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,24 @@
   </si>
   <si>
     <t>Hectic day, stuck in heavy traffic and had a very busy schedule.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>A happy and peaceful day. It was short, less hectic, and I felt relaxed , and positive throughout the day.</t>
+  </si>
+  <si>
+    <t>A hectic day with long hours of studying. I felt bit frustated and tired, but still managed to get through the day ,and complete my work.</t>
+  </si>
+  <si>
+    <t>The day was smooth and went well. Everything felt calm and manageable, and I was able to complete my tasks without much stress.</t>
   </si>
 </sst>
 </file>
@@ -1133,71 +1151,143 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B9" s="14">
+        <v>390</v>
+      </c>
+      <c r="C9" s="14">
+        <v>90</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>350</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B10" s="14">
+        <v>390</v>
+      </c>
+      <c r="C10" s="14">
+        <v>90</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>150</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B11" s="14">
+        <v>390</v>
+      </c>
+      <c r="C11" s="14">
+        <v>90</v>
+      </c>
+      <c r="D11" s="14">
+        <v>150</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Welcome\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1726E68-D7BC-4274-B769-F7D87935900A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,18 @@
   </si>
   <si>
     <t>The day was smooth and went well. Everything felt calm and manageable, and I was able to complete my tasks without much stress.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>The day was spent well and peacefully. I had a relaxing weekend, enjoyed some free time, and felt refreshed and happy by the end of the day.</t>
+  </si>
+  <si>
+    <t>It was niceand relaxing weekend. I enjoyed my day, took some time to rest, and spent the day doing things I liked. Overall, the day went well and felt refreshing.</t>
+  </si>
+  <si>
+    <t>The day was very hectic and stressed. I had a lot of work to manage, which made me feel tired and overwhelmed. Overall, it was a busy and exhausting day.</t>
   </si>
 </sst>
 </file>
@@ -886,7 +898,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -1289,71 +1301,143 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>90</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B13" s="14">
+        <v>390</v>
+      </c>
+      <c r="C13" s="14">
+        <v>90</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>90</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>30</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Welcome\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E7EFBC9-2949-4151-8E7D-720EB44C39BD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t>The day was very hectic and stressed. I had a lot of work to manage, which made me feel tired and overwhelmed. Overall, it was a busy and exhausting day.</t>
+  </si>
+  <si>
+    <t>The day went okay. It was a medium and balanced day- not too hectic and not too relaxing. Overall, it went smoothly.</t>
+  </si>
+  <si>
+    <t>The day was quite hectic and busy. There were many tasks to manage, which made the day feel tiring, but overall, I managed to get through it.</t>
+  </si>
+  <si>
+    <t>The day  went smoothly and easily. It was calm, relaxed, and non-hectic, with everything going at a comfortable pace</t>
   </si>
 </sst>
 </file>
@@ -898,7 +907,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="34.26953125" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -1439,71 +1448,143 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+    <row r="15" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="14">
+        <v>390</v>
+      </c>
+      <c r="C15" s="14">
+        <v>90</v>
+      </c>
+      <c r="D15" s="14">
+        <v>30</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>30</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B16" s="14">
+        <v>390</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>400</v>
+      </c>
+      <c r="G16" s="14">
+        <v>8</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>30</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E7EFBC9-2949-4151-8E7D-720EB44C39BD}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16807C14-FB5A-4112-B1B9-96CA0CF474C5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>The day  went smoothly and easily. It was calm, relaxed, and non-hectic, with everything going at a comfortable pace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The day went well overall. Since Punjab was under a shutdown for the whole day, the day was quiet and mostly spent at home. </t>
+  </si>
+  <si>
+    <t>It was a good weekend. I visited my old university to collect my graduation certificate and marksheet.  Being back there brought back many old memories and made me feel nostalgic.</t>
+  </si>
+  <si>
+    <t>It was a smooth and relaxing weekend. The day went well, and I enjoyed some peaceful time, making it a pleasant and refreshing day.</t>
   </si>
 </sst>
 </file>
@@ -1586,71 +1595,143 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B18" s="14">
+        <v>450</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>360</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B19" s="14">
+        <v>540</v>
+      </c>
+      <c r="C19" s="14">
+        <v>90</v>
+      </c>
+      <c r="D19" s="14">
+        <v>30</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>90</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B20" s="14">
+        <v>600</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16807C14-FB5A-4112-B1B9-96CA0CF474C5}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63FA9196-B17E-4D42-9EC1-9813F40871D3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,18 @@
   </si>
   <si>
     <t>It was a smooth and relaxing weekend. The day went well, and I enjoyed some peaceful time, making it a pleasant and refreshing day.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>The day was very hectic due to a busy and hectic timetable. There were many classes and tasks throughout the day, which made it quite tiring and exhausting.</t>
+  </si>
+  <si>
+    <t>The day was again quite hectic because of the packed timetable. With back-to-back classes and activities, it felt busy and tiring, but the day went well overall.</t>
+  </si>
+  <si>
+    <t>The day was very hectic due to a busy timetable, and I also fell ill. Managing everything while feeling unwell was quite difficult and exhausting, making the day more challenging than usual.</t>
   </si>
 </sst>
 </file>
@@ -1733,71 +1745,143 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A21" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>30</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>30</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>90</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>30</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>90</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63FA9196-B17E-4D42-9EC1-9813F40871D3}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AFCC8F2-ED78-4948-ADB0-EF59BB8FCB64}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>The day was very hectic due to a busy timetable, and I also fell ill. Managing everything while feeling unwell was quite difficult and exhausting, making the day more challenging than usual.</t>
+  </si>
+  <si>
+    <t>The day went well and smoothly. Overall, it was a pleasant and productive day.</t>
+  </si>
+  <si>
+    <t>The day went well and was filled with happiness as I celebrated Rakhi with my family.</t>
   </si>
 </sst>
 </file>
@@ -1883,49 +1889,97 @@
         <v>79</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+    <row r="24" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>40</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>30</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AFCC8F2-ED78-4948-ADB0-EF59BB8FCB64}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC82A62-40D2-43A9-B95C-5DCF4F104DC6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>The day went well and was filled with happiness as I celebrated Rakhi with my family.</t>
+  </si>
+  <si>
+    <t>Spent the day relaxing and enjoying some free time. I took a break from my usual routine and recharged myself for the coming week.</t>
+  </si>
+  <si>
+    <t>Had a peaceful weekened, spent some time with family, and enjoyed a break from my daily routine.</t>
   </si>
 </sst>
 </file>
@@ -1981,49 +1987,97 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B26" s="14">
+        <v>540</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B27" s="14">
+        <v>540</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>30</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC82A62-40D2-43A9-B95C-5DCF4F104DC6}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813745D0-A323-4E0D-9616-E57767CF5B00}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>Had a peaceful weekened, spent some time with family, and enjoyed a break from my daily routine.</t>
+  </si>
+  <si>
+    <t>The day was quite pathetic and damn busy. The hectic schedule made it difficult to manage everything, and by the end of the day, I felt completely exhausted.</t>
+  </si>
+  <si>
+    <t>The day went well overall, but it was quite hectic due to a busy schedule. Despite being tired, I managed to complete my tasks and ended the day on a positive note.</t>
   </si>
 </sst>
 </file>
@@ -2079,49 +2085,97 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+    <row r="28" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>30</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>30</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{813745D0-A323-4E0D-9616-E57767CF5B00}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8626B0FD-F029-401E-AC54-65B6D10CDCE7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>The day went well overall, but it was quite hectic due to a busy schedule. Despite being tired, I managed to complete my tasks and ended the day on a positive note.</t>
+  </si>
+  <si>
+    <t>The day went well and was quite productive. Overall, everything went smoothly, and I had a good day.</t>
   </si>
 </sst>
 </file>
@@ -2177,27 +2180,51 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+    <row r="30" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>30</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8626B0FD-F029-401E-AC54-65B6D10CDCE7}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C13D8229-06C6-43AE-9E85-ED97BEC4C3F4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>The day went well and was quite productive. Overall, everything went smoothly, and I had a good day.</t>
+  </si>
+  <si>
+    <t>Today was a good day overall. Everything went well, and I was able to manage my tasks smoothly.</t>
   </si>
 </sst>
 </file>
@@ -2226,27 +2229,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+    <row r="31" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>30</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>100</v>
+      </c>
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>740</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C13D8229-06C6-43AE-9E85-ED97BEC4C3F4}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18A5A608-7E06-4467-BF8E-1D9EE79051EB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Today was a good day overall. Everything went well, and I was able to manage my tasks smoothly.</t>
+  </si>
+  <si>
+    <t>Everything went smoothly today. The day was well managed, and overall, it went really well.</t>
   </si>
 </sst>
 </file>
@@ -2275,27 +2278,51 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+    <row r="32" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>30</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14">
+        <v>3</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18A5A608-7E06-4467-BF8E-1D9EE79051EB}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24555D95-CA85-490A-B0B5-B239E6249DF4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,12 @@
   </si>
   <si>
     <t>Everything went smoothly today. The day was well managed, and overall, it went really well.</t>
+  </si>
+  <si>
+    <t>The weekend was relaxing and peaceful. I took some time to rest, spend time with family, and enjoy a break from my busy routine. Overall, it was a refreshing and pleasant day.</t>
+  </si>
+  <si>
+    <t>The weekend was calm and enjoyable. I spent the day relaxing, catching up on some personal work, and enjoying some quality time with family. Overall, it was a nice and refreshing day.</t>
   </si>
 </sst>
 </file>
@@ -2324,49 +2330,97 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B33" s="14">
+        <v>520</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B34" s="14">
+        <v>520</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24555D95-CA85-490A-B0B5-B239E6249DF4}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6AC03DA-6BCC-476F-BEA8-7354E7C240FA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,102 +212,6 @@
   </si>
   <si>
     <t>As, I had an exam today ,and had to travel afterward. I was a little tired, but I managed to complete my momentous tasks and get some rest.</t>
-  </si>
-  <si>
-    <t>Hectic day, stuck in heavy traffic and had a very busy schedule.</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Excellent</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>A happy and peaceful day. It was short, less hectic, and I felt relaxed , and positive throughout the day.</t>
-  </si>
-  <si>
-    <t>A hectic day with long hours of studying. I felt bit frustated and tired, but still managed to get through the day ,and complete my work.</t>
-  </si>
-  <si>
-    <t>The day was smooth and went well. Everything felt calm and manageable, and I was able to complete my tasks without much stress.</t>
-  </si>
-  <si>
-    <t>Very Satisfied</t>
-  </si>
-  <si>
-    <t>The day was spent well and peacefully. I had a relaxing weekend, enjoyed some free time, and felt refreshed and happy by the end of the day.</t>
-  </si>
-  <si>
-    <t>It was niceand relaxing weekend. I enjoyed my day, took some time to rest, and spent the day doing things I liked. Overall, the day went well and felt refreshing.</t>
-  </si>
-  <si>
-    <t>The day was very hectic and stressed. I had a lot of work to manage, which made me feel tired and overwhelmed. Overall, it was a busy and exhausting day.</t>
-  </si>
-  <si>
-    <t>The day went okay. It was a medium and balanced day- not too hectic and not too relaxing. Overall, it went smoothly.</t>
-  </si>
-  <si>
-    <t>The day was quite hectic and busy. There were many tasks to manage, which made the day feel tiring, but overall, I managed to get through it.</t>
-  </si>
-  <si>
-    <t>The day  went smoothly and easily. It was calm, relaxed, and non-hectic, with everything going at a comfortable pace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The day went well overall. Since Punjab was under a shutdown for the whole day, the day was quiet and mostly spent at home. </t>
-  </si>
-  <si>
-    <t>It was a good weekend. I visited my old university to collect my graduation certificate and marksheet.  Being back there brought back many old memories and made me feel nostalgic.</t>
-  </si>
-  <si>
-    <t>It was a smooth and relaxing weekend. The day went well, and I enjoyed some peaceful time, making it a pleasant and refreshing day.</t>
-  </si>
-  <si>
-    <t>Unsatisfied</t>
-  </si>
-  <si>
-    <t>The day was very hectic due to a busy and hectic timetable. There were many classes and tasks throughout the day, which made it quite tiring and exhausting.</t>
-  </si>
-  <si>
-    <t>The day was again quite hectic because of the packed timetable. With back-to-back classes and activities, it felt busy and tiring, but the day went well overall.</t>
-  </si>
-  <si>
-    <t>The day was very hectic due to a busy timetable, and I also fell ill. Managing everything while feeling unwell was quite difficult and exhausting, making the day more challenging than usual.</t>
-  </si>
-  <si>
-    <t>The day went well and smoothly. Overall, it was a pleasant and productive day.</t>
-  </si>
-  <si>
-    <t>The day went well and was filled with happiness as I celebrated Rakhi with my family.</t>
-  </si>
-  <si>
-    <t>Spent the day relaxing and enjoying some free time. I took a break from my usual routine and recharged myself for the coming week.</t>
-  </si>
-  <si>
-    <t>Had a peaceful weekened, spent some time with family, and enjoyed a break from my daily routine.</t>
-  </si>
-  <si>
-    <t>The day was quite pathetic and damn busy. The hectic schedule made it difficult to manage everything, and by the end of the day, I felt completely exhausted.</t>
-  </si>
-  <si>
-    <t>The day went well overall, but it was quite hectic due to a busy schedule. Despite being tired, I managed to complete my tasks and ended the day on a positive note.</t>
-  </si>
-  <si>
-    <t>The day went well and was quite productive. Overall, everything went smoothly, and I had a good day.</t>
-  </si>
-  <si>
-    <t>Today was a good day overall. Everything went well, and I was able to manage my tasks smoothly.</t>
-  </si>
-  <si>
-    <t>Everything went smoothly today. The day was well managed, and overall, it went really well.</t>
-  </si>
-  <si>
-    <t>The weekend was relaxing and peaceful. I took some time to rest, spend time with family, and enjoy a break from my busy routine. Overall, it was a refreshing and pleasant day.</t>
-  </si>
-  <si>
-    <t>The weekend was calm and enjoyable. I spent the day relaxing, catching up on some personal work, and enjoying some quality time with family. Overall, it was a nice and refreshing day.</t>
   </si>
 </sst>
 </file>
@@ -961,7 +865,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" customWidth="1"/>
+    <col min="1" max="1" width="17.1796875" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -1180,1247 +1084,599 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
-        <v>46245</v>
-      </c>
-      <c r="B8" s="14">
-        <v>420</v>
-      </c>
-      <c r="C8" s="14">
-        <v>120</v>
-      </c>
-      <c r="D8" s="14">
-        <v>60</v>
-      </c>
-      <c r="E8" s="14">
-        <v>90</v>
-      </c>
-      <c r="F8" s="14">
-        <v>300</v>
-      </c>
-      <c r="G8" s="14">
-        <v>5</v>
-      </c>
-      <c r="H8" s="14">
-        <v>30</v>
-      </c>
-      <c r="I8" s="15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="J8" s="15">
+        <v/>
+      </c>
+      <c r="J8" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
-        <v>46246</v>
-      </c>
-      <c r="B9" s="14">
-        <v>390</v>
-      </c>
-      <c r="C9" s="14">
-        <v>90</v>
-      </c>
-      <c r="D9" s="14">
-        <v>120</v>
-      </c>
-      <c r="E9" s="14">
-        <v>60</v>
-      </c>
-      <c r="F9" s="14">
-        <v>350</v>
-      </c>
-      <c r="G9" s="14">
-        <v>7</v>
-      </c>
-      <c r="H9" s="14">
-        <v>60</v>
-      </c>
-      <c r="I9" s="15">
+        <v/>
+      </c>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="17"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1070</v>
-      </c>
-      <c r="J9" s="15">
+        <v/>
+      </c>
+      <c r="J9" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>370</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <v>46247</v>
-      </c>
-      <c r="B10" s="14">
-        <v>390</v>
-      </c>
-      <c r="C10" s="14">
-        <v>90</v>
-      </c>
-      <c r="D10" s="14">
-        <v>120</v>
-      </c>
-      <c r="E10" s="14">
-        <v>30</v>
-      </c>
-      <c r="F10" s="14">
-        <v>150</v>
-      </c>
-      <c r="G10" s="14">
-        <v>3</v>
-      </c>
-      <c r="H10" s="14">
-        <v>60</v>
-      </c>
-      <c r="I10" s="15">
+        <v/>
+      </c>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="17"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>840</v>
-      </c>
-      <c r="J10" s="15">
+        <v/>
+      </c>
+      <c r="J10" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
-        <v>46248</v>
-      </c>
-      <c r="B11" s="14">
-        <v>390</v>
-      </c>
-      <c r="C11" s="14">
-        <v>90</v>
-      </c>
-      <c r="D11" s="14">
-        <v>150</v>
-      </c>
-      <c r="E11" s="14">
-        <v>30</v>
-      </c>
-      <c r="F11" s="14">
-        <v>250</v>
-      </c>
-      <c r="G11" s="14">
-        <v>5</v>
-      </c>
-      <c r="H11" s="14">
-        <v>60</v>
-      </c>
-      <c r="I11" s="15">
+        <v/>
+      </c>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="17"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J11" s="15">
+        <v/>
+      </c>
+      <c r="J11" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>470</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
-        <v>46249</v>
-      </c>
-      <c r="B12" s="14">
-        <v>420</v>
-      </c>
-      <c r="C12" s="14">
-        <v>90</v>
-      </c>
-      <c r="D12" s="14">
-        <v>120</v>
-      </c>
-      <c r="E12" s="14">
-        <v>60</v>
-      </c>
-      <c r="F12" s="14">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14">
-        <v>0</v>
-      </c>
-      <c r="H12" s="14">
-        <v>60</v>
-      </c>
-      <c r="I12" s="15">
+        <v/>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>750</v>
-      </c>
-      <c r="J12" s="15">
+        <v/>
+      </c>
+      <c r="J12" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>690</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
-        <v>46250</v>
-      </c>
-      <c r="B13" s="14">
-        <v>390</v>
-      </c>
-      <c r="C13" s="14">
-        <v>90</v>
-      </c>
-      <c r="D13" s="14">
-        <v>120</v>
-      </c>
-      <c r="E13" s="14">
-        <v>30</v>
-      </c>
-      <c r="F13" s="14">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14">
-        <v>60</v>
-      </c>
-      <c r="I13" s="15">
+        <v/>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="17"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J13" s="15">
+        <v/>
+      </c>
+      <c r="J13" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
-        <v>46251</v>
-      </c>
-      <c r="B14" s="14">
-        <v>420</v>
-      </c>
-      <c r="C14" s="14">
-        <v>90</v>
-      </c>
-      <c r="D14" s="14">
-        <v>60</v>
-      </c>
-      <c r="E14" s="14">
-        <v>30</v>
-      </c>
-      <c r="F14" s="14">
-        <v>350</v>
-      </c>
-      <c r="G14" s="14">
-        <v>7</v>
-      </c>
-      <c r="H14" s="14">
-        <v>30</v>
-      </c>
-      <c r="I14" s="15">
+        <v/>
+      </c>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="17"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J14" s="15">
+        <v/>
+      </c>
+      <c r="J14" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>460</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
-        <v>46252</v>
-      </c>
-      <c r="B15" s="14">
-        <v>390</v>
-      </c>
-      <c r="C15" s="14">
-        <v>90</v>
-      </c>
-      <c r="D15" s="14">
-        <v>30</v>
-      </c>
-      <c r="E15" s="14">
-        <v>30</v>
-      </c>
-      <c r="F15" s="14">
-        <v>200</v>
-      </c>
-      <c r="G15" s="14">
-        <v>4</v>
-      </c>
-      <c r="H15" s="14">
-        <v>30</v>
-      </c>
-      <c r="I15" s="15">
+        <v/>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>770</v>
-      </c>
-      <c r="J15" s="15">
+        <v/>
+      </c>
+      <c r="J15" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>670</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
-        <v>46253</v>
-      </c>
-      <c r="B16" s="14">
-        <v>390</v>
-      </c>
-      <c r="C16" s="14">
-        <v>60</v>
-      </c>
-      <c r="D16" s="14">
-        <v>60</v>
-      </c>
-      <c r="E16" s="14">
-        <v>30</v>
-      </c>
-      <c r="F16" s="14">
-        <v>400</v>
-      </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="14">
-        <v>30</v>
-      </c>
-      <c r="I16" s="15">
+        <v/>
+      </c>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="13"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J16" s="15">
+        <v/>
+      </c>
+      <c r="J16" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>470</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
-        <v>46254</v>
-      </c>
-      <c r="B17" s="14">
-        <v>420</v>
-      </c>
-      <c r="C17" s="14">
-        <v>60</v>
-      </c>
-      <c r="D17" s="14">
-        <v>30</v>
-      </c>
-      <c r="E17" s="14">
-        <v>30</v>
-      </c>
-      <c r="F17" s="14">
-        <v>150</v>
-      </c>
-      <c r="G17" s="14">
-        <v>3</v>
-      </c>
-      <c r="H17" s="14">
-        <v>30</v>
-      </c>
-      <c r="I17" s="15">
+        <v/>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>720</v>
-      </c>
-      <c r="J17" s="15">
+        <v/>
+      </c>
+      <c r="J17" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
-        <v>46255</v>
-      </c>
-      <c r="B18" s="14">
-        <v>450</v>
-      </c>
-      <c r="C18" s="14">
-        <v>30</v>
-      </c>
-      <c r="D18" s="14">
-        <v>360</v>
-      </c>
-      <c r="E18" s="14">
-        <v>30</v>
-      </c>
-      <c r="F18" s="14">
-        <v>0</v>
-      </c>
-      <c r="G18" s="14">
-        <v>0</v>
-      </c>
-      <c r="H18" s="14">
-        <v>60</v>
-      </c>
-      <c r="I18" s="15">
+        <v/>
+      </c>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>930</v>
-      </c>
-      <c r="J18" s="15">
+        <v/>
+      </c>
+      <c r="J18" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>510</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="13">
-        <v>46256</v>
-      </c>
-      <c r="B19" s="14">
-        <v>540</v>
-      </c>
-      <c r="C19" s="14">
-        <v>90</v>
-      </c>
-      <c r="D19" s="14">
-        <v>30</v>
-      </c>
-      <c r="E19" s="14">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14">
-        <v>0</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0</v>
-      </c>
-      <c r="H19" s="14">
-        <v>90</v>
-      </c>
-      <c r="I19" s="15">
+        <v/>
+      </c>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="17"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="13"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>750</v>
-      </c>
-      <c r="J19" s="15">
+        <v/>
+      </c>
+      <c r="J19" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>690</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L19" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M19" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="13">
-        <v>46257</v>
-      </c>
-      <c r="B20" s="14">
-        <v>600</v>
-      </c>
-      <c r="C20" s="14">
-        <v>60</v>
-      </c>
-      <c r="D20" s="14">
-        <v>60</v>
-      </c>
-      <c r="E20" s="14">
-        <v>60</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>60</v>
-      </c>
-      <c r="I20" s="15">
+        <v/>
+      </c>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="17"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>840</v>
-      </c>
-      <c r="J20" s="15">
+        <v/>
+      </c>
+      <c r="J20" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>600</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A21" s="13">
-        <v>46319</v>
-      </c>
-      <c r="B21" s="14">
-        <v>420</v>
-      </c>
-      <c r="C21" s="14">
-        <v>60</v>
-      </c>
-      <c r="D21" s="14">
-        <v>30</v>
-      </c>
-      <c r="E21" s="14">
-        <v>30</v>
-      </c>
-      <c r="F21" s="14">
-        <v>350</v>
-      </c>
-      <c r="G21" s="14">
-        <v>7</v>
-      </c>
-      <c r="H21" s="14">
-        <v>60</v>
-      </c>
-      <c r="I21" s="15">
+        <v/>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="17"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J21" s="15">
+        <v/>
+      </c>
+      <c r="J21" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N21" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A22" s="13">
-        <v>46259</v>
-      </c>
-      <c r="B22" s="14">
-        <v>420</v>
-      </c>
-      <c r="C22" s="14">
-        <v>60</v>
-      </c>
-      <c r="D22" s="14">
-        <v>30</v>
-      </c>
-      <c r="E22" s="14">
-        <v>30</v>
-      </c>
-      <c r="F22" s="14">
-        <v>300</v>
-      </c>
-      <c r="G22" s="14">
-        <v>6</v>
-      </c>
-      <c r="H22" s="14">
-        <v>90</v>
-      </c>
-      <c r="I22" s="15">
+        <v/>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="17"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>930</v>
-      </c>
-      <c r="J22" s="15">
+        <v/>
+      </c>
+      <c r="J22" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>510</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N22" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A23" s="13">
-        <v>46260</v>
-      </c>
-      <c r="B23" s="14">
-        <v>420</v>
-      </c>
-      <c r="C23" s="14">
-        <v>60</v>
-      </c>
-      <c r="D23" s="14">
-        <v>30</v>
-      </c>
-      <c r="E23" s="14">
-        <v>30</v>
-      </c>
-      <c r="F23" s="14">
-        <v>350</v>
-      </c>
-      <c r="G23" s="14">
-        <v>7</v>
-      </c>
-      <c r="H23" s="14">
-        <v>90</v>
-      </c>
-      <c r="I23" s="15">
+        <v/>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J23" s="15">
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>460</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="13">
-        <v>46261</v>
-      </c>
-      <c r="B24" s="14">
-        <v>420</v>
-      </c>
-      <c r="C24" s="14">
-        <v>60</v>
-      </c>
-      <c r="D24" s="14">
-        <v>40</v>
-      </c>
-      <c r="E24" s="14">
-        <v>30</v>
-      </c>
-      <c r="F24" s="14">
-        <v>200</v>
-      </c>
-      <c r="G24" s="14">
-        <v>4</v>
-      </c>
-      <c r="H24" s="14">
-        <v>60</v>
-      </c>
-      <c r="I24" s="15">
+        <v/>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="17"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="13"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>810</v>
-      </c>
-      <c r="J24" s="15">
+        <v/>
+      </c>
+      <c r="J24" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>630</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A25" s="13">
-        <v>46262</v>
-      </c>
-      <c r="B25" s="14">
-        <v>420</v>
-      </c>
-      <c r="C25" s="14">
-        <v>60</v>
-      </c>
-      <c r="D25" s="14">
-        <v>30</v>
-      </c>
-      <c r="E25" s="14">
-        <v>30</v>
-      </c>
-      <c r="F25" s="14">
-        <v>150</v>
-      </c>
-      <c r="G25" s="14">
-        <v>3</v>
-      </c>
-      <c r="H25" s="14">
-        <v>60</v>
-      </c>
-      <c r="I25" s="15">
+        <v/>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="17"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>750</v>
-      </c>
-      <c r="J25" s="15">
+        <v/>
+      </c>
+      <c r="J25" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>690</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M25" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="13">
-        <v>46263</v>
-      </c>
-      <c r="B26" s="14">
-        <v>540</v>
-      </c>
-      <c r="C26" s="14">
-        <v>60</v>
-      </c>
-      <c r="D26" s="14">
-        <v>60</v>
-      </c>
-      <c r="E26" s="14">
-        <v>30</v>
-      </c>
-      <c r="F26" s="14">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>0</v>
-      </c>
-      <c r="H26" s="14">
-        <v>60</v>
-      </c>
-      <c r="I26" s="15">
+        <v/>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="17"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>750</v>
-      </c>
-      <c r="J26" s="15">
+        <v/>
+      </c>
+      <c r="J26" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>690</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M26" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A27" s="13">
-        <v>46264</v>
-      </c>
-      <c r="B27" s="14">
-        <v>540</v>
-      </c>
-      <c r="C27" s="14">
-        <v>60</v>
-      </c>
-      <c r="D27" s="14">
-        <v>30</v>
-      </c>
-      <c r="E27" s="14">
-        <v>30</v>
-      </c>
-      <c r="F27" s="14">
-        <v>0</v>
-      </c>
-      <c r="G27" s="14">
-        <v>0</v>
-      </c>
-      <c r="H27" s="14">
-        <v>60</v>
-      </c>
-      <c r="I27" s="15">
+        <v/>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="17"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>720</v>
-      </c>
-      <c r="J27" s="15">
+        <v/>
+      </c>
+      <c r="J27" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M27" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N27" s="17" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A28" s="13">
-        <v>46265</v>
-      </c>
-      <c r="B28" s="14">
-        <v>420</v>
-      </c>
-      <c r="C28" s="14">
-        <v>60</v>
-      </c>
-      <c r="D28" s="14">
-        <v>30</v>
-      </c>
-      <c r="E28" s="14">
-        <v>30</v>
-      </c>
-      <c r="F28" s="14">
-        <v>350</v>
-      </c>
-      <c r="G28" s="14">
-        <v>7</v>
-      </c>
-      <c r="H28" s="14">
-        <v>60</v>
-      </c>
-      <c r="I28" s="15">
+        <v/>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="17"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="13"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J28" s="15">
+        <v/>
+      </c>
+      <c r="J28" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L28" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M28" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N28" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A29" s="13">
-        <v>46266</v>
-      </c>
-      <c r="B29" s="14">
-        <v>420</v>
-      </c>
-      <c r="C29" s="14">
-        <v>60</v>
-      </c>
-      <c r="D29" s="14">
-        <v>30</v>
-      </c>
-      <c r="E29" s="14">
-        <v>30</v>
-      </c>
-      <c r="F29" s="14">
-        <v>300</v>
-      </c>
-      <c r="G29" s="14">
-        <v>6</v>
-      </c>
-      <c r="H29" s="14">
-        <v>60</v>
-      </c>
-      <c r="I29" s="15">
+        <v/>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="17"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="13"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J29" s="15">
+        <v/>
+      </c>
+      <c r="J29" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="K29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="13">
-        <v>46267</v>
-      </c>
-      <c r="B30" s="14">
-        <v>420</v>
-      </c>
-      <c r="C30" s="14">
-        <v>60</v>
-      </c>
-      <c r="D30" s="14">
-        <v>30</v>
-      </c>
-      <c r="E30" s="14">
-        <v>30</v>
-      </c>
-      <c r="F30" s="14">
-        <v>350</v>
-      </c>
-      <c r="G30" s="14">
-        <v>7</v>
-      </c>
-      <c r="H30" s="14">
-        <v>60</v>
-      </c>
-      <c r="I30" s="15">
+        <v/>
+      </c>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="17"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="13"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="J30" s="15">
+        <v/>
+      </c>
+      <c r="J30" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="M30" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="N30" s="17" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A31" s="13">
-        <v>46268</v>
-      </c>
-      <c r="B31" s="14">
-        <v>420</v>
-      </c>
-      <c r="C31" s="14">
-        <v>60</v>
-      </c>
-      <c r="D31" s="14">
-        <v>30</v>
-      </c>
-      <c r="E31" s="14">
-        <v>30</v>
-      </c>
-      <c r="F31" s="14">
-        <v>100</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
-      <c r="H31" s="14">
-        <v>60</v>
-      </c>
-      <c r="I31" s="15">
+        <v/>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="17"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>700</v>
-      </c>
-      <c r="J31" s="15">
+        <v/>
+      </c>
+      <c r="J31" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>740</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" ht="58" x14ac:dyDescent="0.35">
-      <c r="A32" s="13">
-        <v>46269</v>
-      </c>
-      <c r="B32" s="14">
-        <v>420</v>
-      </c>
-      <c r="C32" s="14">
-        <v>60</v>
-      </c>
-      <c r="D32" s="14">
-        <v>30</v>
-      </c>
-      <c r="E32" s="14">
-        <v>30</v>
-      </c>
-      <c r="F32" s="14">
-        <v>150</v>
-      </c>
-      <c r="G32" s="14">
-        <v>3</v>
-      </c>
-      <c r="H32" s="14">
-        <v>30</v>
-      </c>
-      <c r="I32" s="15">
+        <v/>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="17"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>720</v>
-      </c>
-      <c r="J32" s="15">
+        <v/>
+      </c>
+      <c r="J32" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="87" x14ac:dyDescent="0.35">
-      <c r="A33" s="13">
-        <v>46270</v>
-      </c>
-      <c r="B33" s="14">
-        <v>520</v>
-      </c>
-      <c r="C33" s="14">
-        <v>60</v>
-      </c>
-      <c r="D33" s="14">
-        <v>120</v>
-      </c>
-      <c r="E33" s="14">
-        <v>60</v>
-      </c>
-      <c r="F33" s="14">
-        <v>0</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14">
-        <v>60</v>
-      </c>
-      <c r="I33" s="15">
+        <v/>
+      </c>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="17"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="13"/>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="J33" s="15">
+        <v/>
+      </c>
+      <c r="J33" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>620</v>
-      </c>
-      <c r="K33" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L33" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="13">
-        <v>46271</v>
-      </c>
-      <c r="B34" s="14">
-        <v>520</v>
-      </c>
-      <c r="C34" s="14">
-        <v>60</v>
-      </c>
-      <c r="D34" s="14">
-        <v>120</v>
-      </c>
-      <c r="E34" s="14">
-        <v>60</v>
-      </c>
-      <c r="F34" s="14">
-        <v>0</v>
-      </c>
-      <c r="G34" s="14">
-        <v>0</v>
-      </c>
-      <c r="H34" s="14">
-        <v>60</v>
-      </c>
-      <c r="I34" s="15">
+        <v/>
+      </c>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="17"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="J34" s="15">
+        <v/>
+      </c>
+      <c r="J34" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>620</v>
-      </c>
-      <c r="K34" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>90</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{121A8414-EF16-466D-AB94-0F94A65433CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6AC03DA-6BCC-476F-BEA8-7354E7C240FA}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32C90A12-A108-465C-8969-E87DB9E22378}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -205,13 +205,118 @@
     <t>MCA(Sec-B)</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>Neutral</t>
   </si>
   <si>
     <t>As, I had an exam today ,and had to travel afterward. I was a little tired, but I managed to complete my momentous tasks and get some rest.</t>
+  </si>
+  <si>
+    <t>Hectic day, stuck in heavy traffic and had a very busy schedule.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>A happy and peaceful day. It was short, less hectic, and I felt relaxed , and positive throughout the day.</t>
+  </si>
+  <si>
+    <t>A hectic day with long hours of studying. I felt bit frustated and tired, but still managed to get through the day ,and complete my work.</t>
+  </si>
+  <si>
+    <t>The day was smooth and went well. Everything felt calm and manageable, and I was able to complete my tasks without much stress.</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>The day was spent well and peacefully. I had a relaxing weekend, enjoyed some free time, and felt refreshed and happy by the end of the day.</t>
+  </si>
+  <si>
+    <t>It was niceand relaxing weekend. I enjoyed my day, took some time to rest, and spent the day doing things I liked. Overall, the day went well and felt refreshing.</t>
+  </si>
+  <si>
+    <t>The day was very hectic and stressed. I had a lot of work to manage, which made me feel tired and overwhelmed. Overall, it was a busy and exhausting day.</t>
+  </si>
+  <si>
+    <t>The day went okay. It was a medium and balanced day- not too hectic and not too relaxing. Overall, it went smoothly.</t>
+  </si>
+  <si>
+    <t>The day was quite hectic and busy. There were many tasks to manage, which made the day feel tiring, but overall, I managed to get through it.</t>
+  </si>
+  <si>
+    <t>The day  went smoothly and easily. It was calm, relaxed, and non-hectic, with everything going at a comfortable pace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The day went well overall. Since Punjab was under a shutdown for the whole day, the day was quiet and mostly spent at home. </t>
+  </si>
+  <si>
+    <t>It was a good weekend. I visited my old university to collect my graduation certificate and marksheet.  Being back there brought back many old memories and made me feel nostalgic.</t>
+  </si>
+  <si>
+    <t>It was a smooth and relaxing weekend. The day went well, and I enjoyed some peaceful time, making it a pleasant and refreshing day.</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>The day was very hectic due to a busy and hectic timetable. There were many classes and tasks throughout the day, which made it quite tiring and exhausting.</t>
+  </si>
+  <si>
+    <t>The day was again quite hectic because of the packed timetable. With back-to-back classes and activities, it felt busy and tiring, but the day went well overall.</t>
+  </si>
+  <si>
+    <t>The day was very hectic due to a busy timetable, and I also fell ill. Managing everything while feeling unwell was quite difficult and exhausting, making the day more challenging than usual.</t>
+  </si>
+  <si>
+    <t>The day went well and smoothly. Overall, it was a pleasant and productive day.</t>
+  </si>
+  <si>
+    <t>The day went well and was filled with happiness as I celebrated Rakhi with my family.</t>
+  </si>
+  <si>
+    <t>Spent the day relaxing and enjoying some free time. I took a break from my usual routine and recharged myself for the coming week.</t>
+  </si>
+  <si>
+    <t>Had a peaceful weekened, spent some time with family, and enjoyed a break from my daily routine.</t>
+  </si>
+  <si>
+    <t>The day was quite pathetic and damn busy. The hectic schedule made it difficult to manage everything, and by the end of the day, I felt completely exhausted.</t>
+  </si>
+  <si>
+    <t>The day went well overall, but it was quite hectic due to a busy schedule. Despite being tired, I managed to complete my tasks and ended the day on a positive note.</t>
+  </si>
+  <si>
+    <t>The day went well and was quite productive. Overall, everything went smoothly, and I had a good day.</t>
+  </si>
+  <si>
+    <t>Today was a good day overall. Everything went well, and I was able to manage my tasks smoothly.</t>
+  </si>
+  <si>
+    <t>Everything went smoothly today. The day was well managed, and overall, it went really well.</t>
+  </si>
+  <si>
+    <t>The weekend was relaxing and peaceful. I took some time to rest, spend time with family, and enjoy a break from my busy routine. Overall, it was a refreshing and pleasant day.</t>
+  </si>
+  <si>
+    <t>The weekend was calm and enjoyable. I spent the day relaxing, catching up on some personal work, and enjoying some quality time with family. Overall, it was a nice and refreshing day.</t>
+  </si>
+  <si>
+    <t>August , September</t>
+  </si>
+  <si>
+    <t>The day was hectic, but managed my work efficiently.</t>
+  </si>
+  <si>
+    <t>The day was fine,full of tiredness.</t>
+  </si>
+  <si>
+    <t>The day was good. Everything went smoothly.</t>
   </si>
 </sst>
 </file>
@@ -865,7 +970,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="34.26953125" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
@@ -926,7 +1031,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1072,7 +1177,7 @@
         <v>370</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>50</v>
@@ -1081,668 +1186,1388 @@
         <v>51</v>
       </c>
       <c r="N7" s="17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>120</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>90</v>
+      </c>
+      <c r="F8" s="14">
+        <v>300</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>1020</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="1"/>
+        <v>420</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="9" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B9" s="14">
+        <v>390</v>
+      </c>
+      <c r="C9" s="14">
+        <v>90</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>60</v>
+      </c>
+      <c r="F9" s="14">
+        <v>350</v>
+      </c>
+      <c r="G9" s="14">
+        <v>7</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+        <v>370</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A10" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B10" s="14">
+        <v>390</v>
+      </c>
+      <c r="C10" s="14">
+        <v>90</v>
+      </c>
+      <c r="D10" s="14">
+        <v>120</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>150</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B11" s="14">
+        <v>390</v>
+      </c>
+      <c r="C11" s="14">
+        <v>90</v>
+      </c>
+      <c r="D11" s="14">
+        <v>150</v>
+      </c>
+      <c r="E11" s="14">
+        <v>30</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B12" s="14">
+        <v>420</v>
+      </c>
+      <c r="C12" s="14">
+        <v>90</v>
+      </c>
+      <c r="D12" s="14">
+        <v>120</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A13" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B13" s="14">
+        <v>390</v>
+      </c>
+      <c r="C13" s="14">
+        <v>90</v>
+      </c>
+      <c r="D13" s="14">
+        <v>120</v>
+      </c>
+      <c r="E13" s="14">
+        <v>30</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A14" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B14" s="14">
+        <v>420</v>
+      </c>
+      <c r="C14" s="14">
+        <v>90</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14">
+        <v>350</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7</v>
+      </c>
+      <c r="H14" s="14">
+        <v>30</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+        <v>460</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A15" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="14">
+        <v>390</v>
+      </c>
+      <c r="C15" s="14">
+        <v>90</v>
+      </c>
+      <c r="D15" s="14">
+        <v>30</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>30</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+        <v>670</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B16" s="14">
+        <v>390</v>
+      </c>
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>60</v>
+      </c>
+      <c r="E16" s="14">
+        <v>30</v>
+      </c>
+      <c r="F16" s="14">
+        <v>400</v>
+      </c>
+      <c r="G16" s="14">
+        <v>8</v>
+      </c>
+      <c r="H16" s="14">
+        <v>30</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B17" s="14">
+        <v>420</v>
+      </c>
+      <c r="C17" s="14">
+        <v>60</v>
+      </c>
+      <c r="D17" s="14">
+        <v>30</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>30</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B18" s="14">
+        <v>450</v>
+      </c>
+      <c r="C18" s="14">
+        <v>30</v>
+      </c>
+      <c r="D18" s="14">
+        <v>360</v>
+      </c>
+      <c r="E18" s="14">
+        <v>30</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B19" s="14">
+        <v>540</v>
+      </c>
+      <c r="C19" s="14">
+        <v>90</v>
+      </c>
+      <c r="D19" s="14">
+        <v>30</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>90</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B20" s="14">
+        <v>600</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>60</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>600</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A21" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>30</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>60</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A22" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>30</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>90</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A23" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>30</v>
+      </c>
+      <c r="E23" s="14">
+        <v>30</v>
+      </c>
+      <c r="F23" s="14">
+        <v>350</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>90</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>460</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B24" s="14">
+        <v>420</v>
+      </c>
+      <c r="C24" s="14">
+        <v>60</v>
+      </c>
+      <c r="D24" s="14">
+        <v>40</v>
+      </c>
+      <c r="E24" s="14">
+        <v>30</v>
+      </c>
+      <c r="F24" s="14">
+        <v>200</v>
+      </c>
+      <c r="G24" s="14">
+        <v>4</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A25" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B25" s="14">
+        <v>420</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>30</v>
+      </c>
+      <c r="E25" s="14">
+        <v>30</v>
+      </c>
+      <c r="F25" s="14">
+        <v>150</v>
+      </c>
+      <c r="G25" s="14">
+        <v>3</v>
+      </c>
+      <c r="H25" s="14">
+        <v>60</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B26" s="14">
+        <v>540</v>
+      </c>
+      <c r="C26" s="14">
+        <v>60</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>30</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>690</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A27" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B27" s="14">
+        <v>540</v>
+      </c>
+      <c r="C27" s="14">
+        <v>60</v>
+      </c>
+      <c r="D27" s="14">
+        <v>30</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A28" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B28" s="14">
+        <v>420</v>
+      </c>
+      <c r="C28" s="14">
+        <v>60</v>
+      </c>
+      <c r="D28" s="14">
+        <v>30</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A29" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B29" s="14">
+        <v>420</v>
+      </c>
+      <c r="C29" s="14">
+        <v>60</v>
+      </c>
+      <c r="D29" s="14">
+        <v>30</v>
+      </c>
+      <c r="E29" s="14">
+        <v>30</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A30" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B30" s="14">
+        <v>420</v>
+      </c>
+      <c r="C30" s="14">
+        <v>60</v>
+      </c>
+      <c r="D30" s="14">
+        <v>30</v>
+      </c>
+      <c r="E30" s="14">
+        <v>30</v>
+      </c>
+      <c r="F30" s="14">
+        <v>350</v>
+      </c>
+      <c r="G30" s="14">
+        <v>7</v>
+      </c>
+      <c r="H30" s="14">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>490</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A31" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B31" s="14">
+        <v>420</v>
+      </c>
+      <c r="C31" s="14">
+        <v>60</v>
+      </c>
+      <c r="D31" s="14">
+        <v>30</v>
+      </c>
+      <c r="E31" s="14">
+        <v>30</v>
+      </c>
+      <c r="F31" s="14">
+        <v>100</v>
+      </c>
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>700</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="58" x14ac:dyDescent="0.35">
+      <c r="A32" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>60</v>
+      </c>
+      <c r="D32" s="14">
+        <v>30</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>150</v>
+      </c>
+      <c r="G32" s="14">
+        <v>3</v>
+      </c>
+      <c r="H32" s="14">
+        <v>30</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+      <c r="A33" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B33" s="14">
+        <v>520</v>
+      </c>
+      <c r="C33" s="14">
+        <v>60</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>60</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>60</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B34" s="14">
+        <v>520</v>
+      </c>
+      <c r="C34" s="14">
+        <v>60</v>
+      </c>
+      <c r="D34" s="14">
+        <v>120</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B35" s="14">
+        <v>420</v>
+      </c>
+      <c r="C35" s="14">
+        <v>60</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>30</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>400</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>40</v>
+      </c>
+      <c r="D36" s="14">
+        <v>120</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>30</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>470</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B37" s="14">
+        <v>520</v>
+      </c>
+      <c r="C37" s="14">
+        <v>60</v>
+      </c>
+      <c r="D37" s="14">
+        <v>60</v>
+      </c>
+      <c r="E37" s="14">
+        <v>60</v>
+      </c>
+      <c r="F37" s="14">
+        <v>350</v>
+      </c>
+      <c r="G37" s="14">
+        <v>7</v>
+      </c>
+      <c r="H37" s="14">
+        <v>60</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>330</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>

--- a/12602848.xlsx
+++ b/12602848.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/223f9e9a821a55c0/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32C90A12-A108-465C-8969-E87DB9E22378}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="13_ncr:1_{33D51D19-ED2F-4213-9176-396229F62C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E44CC576-CC47-4376-93FD-20824385C17B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>The day was good. Everything went smoothly.</t>
+  </si>
+  <si>
+    <t>Today went smoothly. I completed my tasks on time and had a productive and positive day. Overall, it was a good day.</t>
   </si>
 </sst>
 </file>
@@ -2569,27 +2572,51 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+    <row r="38" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B38" s="14">
+        <v>420</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>30</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>100</v>
+      </c>
+      <c r="G38" s="14">
+        <v>2</v>
+      </c>
+      <c r="H38" s="14">
+        <v>50</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>
